--- a/LoanOfficer-A/2026/168 lanchenbi ayanpalli.xlsx
+++ b/LoanOfficer-A/2026/168 lanchenbi ayanpalli.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>8400</v>
+        <v>37800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>63000</v>
+        <v>33600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -938,9 +938,15 @@
       <c r="A5" s="1">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="1"/>
+      <c r="B5" s="3">
+        <v>46115</v>
+      </c>
+      <c r="C5" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
       <c r="E5" s="1">
         <v>33</v>
       </c>
@@ -964,9 +970,15 @@
       <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="1"/>
+      <c r="B6" s="3">
+        <v>46125</v>
+      </c>
+      <c r="C6" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D6" s="1">
+        <v>1</v>
+      </c>
       <c r="E6" s="1">
         <v>34</v>
       </c>
@@ -990,9 +1002,15 @@
       <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="1"/>
+      <c r="B7" s="3">
+        <v>46129</v>
+      </c>
+      <c r="C7" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D7" s="1">
+        <v>1</v>
+      </c>
       <c r="E7" s="1">
         <v>35</v>
       </c>
@@ -1016,9 +1034,15 @@
       <c r="A8" s="1">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="1"/>
+      <c r="B8" s="3">
+        <v>46136</v>
+      </c>
+      <c r="C8" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D8" s="1">
+        <v>1</v>
+      </c>
       <c r="E8" s="1">
         <v>36</v>
       </c>
@@ -1042,9 +1066,15 @@
       <c r="A9" s="1">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="1"/>
+      <c r="B9" s="3">
+        <v>46150</v>
+      </c>
+      <c r="C9" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D9" s="1">
+        <v>1</v>
+      </c>
       <c r="E9" s="1">
         <v>37</v>
       </c>
@@ -1068,9 +1098,15 @@
       <c r="A10" s="1">
         <v>8</v>
       </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="1"/>
+      <c r="B10" s="3">
+        <v>46157</v>
+      </c>
+      <c r="C10" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1</v>
+      </c>
       <c r="E10" s="1">
         <v>38</v>
       </c>
@@ -1094,9 +1130,15 @@
       <c r="A11" s="1">
         <v>9</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="1"/>
+      <c r="B11" s="3">
+        <v>46157</v>
+      </c>
+      <c r="C11" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D11" s="1">
+        <v>1</v>
+      </c>
       <c r="E11" s="1">
         <v>39</v>
       </c>

--- a/LoanOfficer-A/2026/168 lanchenbi ayanpalli.xlsx
+++ b/LoanOfficer-A/2026/168 lanchenbi ayanpalli.xlsx
@@ -819,7 +819,7 @@
       </c>
       <c r="K1" s="10">
         <f>17-K2</f>
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -828,7 +828,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)+SUM(C34:C63)+SUM(G34:G63)+SUM(K34:K63)+SUM(O34:O63)+SUM(C65:C94)</f>
-        <v>37800</v>
+        <v>71400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -857,7 +857,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)+SUM(D34:D63)+SUM(H34:H63)+SUM(P34:P63)+SUM(D65:D91)+SUM(L34:L63)</f>
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -866,7 +866,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>33600</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1162,9 +1162,15 @@
       <c r="A12" s="1">
         <v>10</v>
       </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="1"/>
+      <c r="B12" s="3">
+        <v>46164</v>
+      </c>
+      <c r="C12" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D12" s="1">
+        <v>1</v>
+      </c>
       <c r="E12" s="1">
         <v>40</v>
       </c>
@@ -1188,9 +1194,15 @@
       <c r="A13" s="1">
         <v>11</v>
       </c>
-      <c r="B13" s="3"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="1"/>
+      <c r="B13" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C13" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
       <c r="E13" s="1">
         <v>41</v>
       </c>
@@ -1214,9 +1226,15 @@
       <c r="A14" s="1">
         <v>12</v>
       </c>
-      <c r="B14" s="3"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="1"/>
+      <c r="B14" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C14" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D14" s="1">
+        <v>1</v>
+      </c>
       <c r="E14" s="1">
         <v>42</v>
       </c>
@@ -1240,9 +1258,15 @@
       <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="3"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="1"/>
+      <c r="B15" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C15" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D15" s="1">
+        <v>1</v>
+      </c>
       <c r="E15" s="1">
         <v>43</v>
       </c>
@@ -1266,9 +1290,15 @@
       <c r="A16" s="1">
         <v>14</v>
       </c>
-      <c r="B16" s="3"/>
-      <c r="C16" s="4"/>
-      <c r="D16" s="1"/>
+      <c r="B16" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C16" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D16" s="1">
+        <v>1</v>
+      </c>
       <c r="E16" s="1">
         <v>44</v>
       </c>
@@ -1292,9 +1322,15 @@
       <c r="A17" s="1">
         <v>15</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="4"/>
-      <c r="D17" s="1"/>
+      <c r="B17" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C17" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D17" s="1">
+        <v>1</v>
+      </c>
       <c r="E17" s="1">
         <v>45</v>
       </c>
@@ -1318,9 +1354,15 @@
       <c r="A18" s="1">
         <v>16</v>
       </c>
-      <c r="B18" s="3"/>
-      <c r="C18" s="4"/>
-      <c r="D18" s="1"/>
+      <c r="B18" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C18" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D18" s="1">
+        <v>1</v>
+      </c>
       <c r="E18" s="1">
         <v>46</v>
       </c>
@@ -1344,9 +1386,15 @@
       <c r="A19" s="1">
         <v>17</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="4"/>
-      <c r="D19" s="1"/>
+      <c r="B19" s="3">
+        <v>46171</v>
+      </c>
+      <c r="C19" s="4">
+        <v>4200</v>
+      </c>
+      <c r="D19" s="1">
+        <v>1</v>
+      </c>
       <c r="E19" s="1">
         <v>47</v>
       </c>
